--- a/reports/一级子公司A_现金流量表_2025-06.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-06.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>152646000</v>
+        <v>153409046</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>862524000</v>
+        <v>862378703</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3070549</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>17432515</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1548566</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>8717073</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>769169</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>4356919</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>617774</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3487662</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>462932</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2613692</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>307905</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1743994</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>232146</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1306844</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>153584</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>871917</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>387523</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>2178452</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>192843</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1095225</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>123162</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>692827</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>391400</v>
+        <v>390005</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2211600</v>
+        <v>2211236</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2781000</v>
+        <v>2787277</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>15714000</v>
+        <v>15718561</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>155818400</v>
+        <v>164452481</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>98880000</v>
+        <v>99332387</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>558720000</v>
+        <v>558535633</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1023231</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>5811935</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>775015</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>4357683</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>511997</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2905140</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>386855</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>2179461</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>256633</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1452200</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>193841</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1095537</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16171000</v>
+        <v>16193920</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>91374000</v>
+        <v>91333023</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8240000</v>
+        <v>8216324</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>46560000</v>
+        <v>46580572</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3399000</v>
+        <v>3412694</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>19206000</v>
+        <v>19198530</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>126690000</v>
+        <v>130302897</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>29128400</v>
+        <v>34149584</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>180062</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1080000</v>
+        <v>1079750</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1504937</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>9000000</v>
+        <v>8997011</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>916026</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>5520000</v>
+        <v>5521839</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1684999</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>13930520</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>84000000</v>
+        <v>84019608</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2009019</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>12000000</v>
+        <v>11998276</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>9964156</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>60000000</v>
+        <v>60002335</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>380910</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2280000</v>
+        <v>2279288</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14311430</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12626431</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3517047</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>21000000</v>
+        <v>20995668</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5517571</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>33000000</v>
+        <v>32999893</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5490098</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>33000000</v>
+        <v>32996552</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180039</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1080000</v>
+        <v>1080217</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9214657</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4487184</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27000000</v>
+        <v>27008740</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4518047</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>27000000</v>
+        <v>26990912</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>716578</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>4320000</v>
+        <v>4321360</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>627024</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3780000</v>
+        <v>3780670</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>90356</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>540000</v>
+        <v>539959</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5294118</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3920539</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20298400</v>
+        <v>25443692</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20298400</v>
+        <v>25443692</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
